--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
   <si>
     <t>TODO</t>
   </si>
@@ -202,31 +202,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,60 +248,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,8 +277,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -317,8 +308,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,7 +325,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,181 +354,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,6 +539,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -553,6 +568,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,54 +639,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -647,10 +647,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -659,133 +659,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1457,9 +1457,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>TODO</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>xat：为猫灵族适配盔甲重量</t>
+  </si>
+  <si>
+    <t>xat：微调种族戒指属性</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1463,6 +1466,11 @@
       </c>
       <c r="B37" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17820"/>
+    <workbookView windowHeight="17865"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
   <si>
     <t>TODO</t>
   </si>
@@ -132,7 +132,7 @@
     <t>设置 boss 掉的战利品饰品都是【不朽的】</t>
   </si>
   <si>
-    <t>审查项目所有代码文件【2026年10月17日】</t>
+    <t>审查项目所有（大部分）代码文件【2026年10月17日】</t>
   </si>
   <si>
     <t>xat：添加种族药水配方</t>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>xat：微调种族戒指属性</t>
+  </si>
+  <si>
+    <t>将每个模组的工具函数提取为自己的库函数，并且设置优先加载</t>
+  </si>
+  <si>
+    <t>各个脚本基本独立，模组只依赖自己，移不移都一样；反之会导致模组变动时依赖调整复杂化</t>
   </si>
 </sst>
 </file>
@@ -161,8 +167,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -198,62 +204,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -265,8 +236,82 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,63 +325,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,127 +357,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,55 +531,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,6 +548,74 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -561,54 +635,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -622,26 +648,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -650,10 +656,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,133 +668,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1153,11 +1159,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
-    <col min="3" max="3" width="46.5" customWidth="1"/>
+    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="3" max="3" width="79.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:3">
@@ -1420,9 +1427,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1471,6 +1481,17 @@
     <row r="38" spans="1:1">
       <c r="A38" s="3" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -8,15 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>TODO</t>
   </si>
@@ -160,6 +158,12 @@
   </si>
   <si>
     <t>各个脚本基本独立，模组只依赖自己，移不移都一样；反之会导致模组变动时依赖调整复杂化</t>
+  </si>
+  <si>
+    <t>审查项目所有【战利品（大部分）】代码文件【2026年10月19日】</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -167,10 +171,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -204,27 +208,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -236,6 +239,95 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -244,74 +336,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,29 +351,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -357,181 +361,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,29 +557,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,23 +582,28 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,6 +637,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -656,10 +660,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -668,137 +672,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -809,6 +813,78 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1159,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1168,13 +1244,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1227,7 +1303,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
@@ -1238,7 +1314,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="27" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
@@ -1249,7 +1325,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
@@ -1257,7 +1333,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
@@ -1289,7 +1365,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
@@ -1321,7 +1397,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
@@ -1337,7 +1413,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
@@ -1353,7 +1429,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B23" t="s">
@@ -1361,7 +1437,7 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B24" t="s">
@@ -1380,7 +1456,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B26" t="s">
@@ -1396,7 +1472,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B28" t="s">
@@ -1404,7 +1480,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="16" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
@@ -1412,7 +1488,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B30" t="s">
@@ -1428,7 +1504,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="18" t="s">
         <v>38</v>
       </c>
       <c r="B32" t="s">
@@ -1436,7 +1512,7 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="19" t="s">
         <v>39</v>
       </c>
       <c r="B33" t="s">
@@ -1447,7 +1523,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B34" t="s">
@@ -1455,7 +1531,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B35" t="s">
@@ -1471,7 +1547,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B37" t="s">
@@ -1479,12 +1555,12 @@
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B39" t="s">
@@ -1492,6 +1568,14 @@
       </c>
       <c r="C39" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1499,28 +1583,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1235,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1558,6 +1558,11 @@
       <c r="A38" s="23" t="s">
         <v>45</v>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="24" t="s">
@@ -1576,6 +1581,27 @@
       </c>
       <c r="B40" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>添加：地牢结构模组：毁灭地牢</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>添加：刷怪笼机制调整模组：Ageing Spawners</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>待批阅：添加 UI 模组：自定义游戏加载界面Drippy Loading Screen</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1579,8 +1579,10 @@
       <c r="A40" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>49</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
       </c>
     </row>
     <row r="41">

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -802,7 +802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -886,6 +886,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1235,11 +1238,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
-    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="2" max="2" style="28" width="7.5625" customWidth="1"/>
     <col min="3" max="3" width="79.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1591,6 +1594,11 @@
           <t>添加：地牢结构模组：毁灭地牢</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1598,11 +1606,59 @@
           <t>添加：刷怪笼机制调整模组：Ageing Spawners</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>目前似乎与【大地高塔】模组不兼容</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>待批阅：添加 UI 模组：自定义游戏加载界面Drippy Loading Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>上传【自定义模组】到 CurseForge</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>战力品脚本：毁灭地牢（105 loot）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>添加：YUNG's Extras</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>将：材料、饰品添加到不毁配置怕【物理掉落模组】</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1637,6 +1637,11 @@
           <t>战力品脚本：毁灭地牢（105 loot）</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1653,12 +1658,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>将：材料、饰品添加到不毁配置怕【物理掉落模组】</t>
+          <t>将：【材料、饰品】添加到不毁配置【物理掉落模组】undestroyableItems</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>战利品脚本：YUNG's Extras</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1673,6 +1673,11 @@
           <t>战利品脚本：YUNG's Extras</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t/>
+          <t>完成</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1630,6 +1630,11 @@
           <t>上传【自定义模组】到 CurseForge</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1676,6 +1681,13 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>等待【自定义模组】通过审核后填写到模组清单</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1691,6 +1691,13 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>添加打包脚本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1690,11 +1690,21 @@
           <t>等待【自定义模组】通过审核后填写到模组清单</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>添加打包脚本</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TODO</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1623,6 +1623,11 @@
           <t>待批阅：添加 UI 模组：自定义游戏加载界面Drippy Loading Screen</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1704,7 +1709,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>添加打包脚本配置</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>工具脚本改为 Logger 类</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1731,6 +1731,11 @@
           <t>工具脚本改为 Logger 类</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t/>
+          <t>完成</t>
         </is>
       </c>
     </row>
@@ -1734,6 +1734,13 @@
       <c r="B52" t="inlineStr">
         <is>
           <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>添加服务器环境</t>
         </is>
       </c>
     </row>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1743,6 +1743,40 @@
           <t>添加服务器环境</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>移除</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>只需要按照服务即可，这是客户端环境，如果运行服务端有些模组会导致崩溃</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bug：修复模组【Dragon Blessings】服务端崩溃问题（尝试加载客户端的粒子类）</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>更新：模组【Dragon Blessings】</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1778,6 +1778,42 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>添加：模组【恐怖生物】</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>添加：模组【真菌感染：孢子】</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>添加：模组【失落的城市】</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1238,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="90.625" customWidth="1"/>
@@ -1814,6 +1814,58 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>添加：模组【技能！重铸 Reskillable Reimagined】</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>修改：模组【恐怖生物】</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>修改：模组【真菌感染：孢子】</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>修改：模组【技能！重铸 Reskillable Reimagined】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>修改：模组【失落的城市】</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>添加：模组【个性伤害数字显示】</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/.manifest/todos.xlsx
+++ b/.manifest/todos.xlsx
@@ -1853,6 +1853,11 @@
           <t>修改：模组【失落的城市】</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>移除</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
